--- a/output/pdf_financials_xlsx/SOIL.xlsx
+++ b/output/pdf_financials_xlsx/SOIL.xlsx
@@ -1644,16 +1644,16 @@
         <v>7.216131</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>4.523</v>
+        <v>4.611717</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.226</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>46.035</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>148.911</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
@@ -1688,16 +1688,16 @@
         <v>-0.542038</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.235</v>
+        <v>-3.146283</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-51.432</v>
+        <v>-67.658</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>114.984</v>
+        <v>68.949</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>477.81</v>
+        <v>328.899</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -1736,16 +1736,16 @@
         <v>-3.184620045060977</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-45.16894722144652</v>
+        <v>-43.93022898631667</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-52.39395297665131</v>
+        <v>-68.92343425288293</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>35.54461934143657</v>
+        <v>21.31397376132949</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>76.50002881899748</v>
+        <v>52.65855251781974</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -4570,22 +4570,22 @@
         <v>7.216131</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>4.523</v>
+        <v>4.522818</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>16.226</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>46.035</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>148.911</v>
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>229.028</v>
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>300.369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -21882,7 +21882,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -26269,7 +26269,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -28225,7 +28225,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -38536,7 +38536,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -41141,7 +41141,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -43393,7 +43393,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">

--- a/output/pdf_financials_xlsx/SOIL.xlsx
+++ b/output/pdf_financials_xlsx/SOIL.xlsx
@@ -1644,16 +1644,16 @@
         <v>7.216131</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>4.611717</v>
+        <v>4.523</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>16.226</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>46.035</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>148.911</v>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
@@ -1688,16 +1688,16 @@
         <v>-0.542038</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.146283</v>
+        <v>-3.235</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-67.658</v>
+        <v>-51.432</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>68.949</v>
+        <v>114.984</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>328.899</v>
+        <v>477.81</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -1736,16 +1736,16 @@
         <v>-3.184620045060977</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-43.93022898631667</v>
+        <v>-45.16894722144652</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-68.92343425288293</v>
+        <v>-52.39395297665131</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>21.31397376132949</v>
+        <v>35.54461934143657</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>52.65855251781974</v>
+        <v>76.50002881899748</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.772925</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.190719</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.747241</v>
@@ -1879,19 +1879,19 @@
         <v>1.110303</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.569111</v>
+        <v>1.11</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.415</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>10.256</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>26.46</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>48.418</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.1225</v>
+        <v>0.895425</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.06</v>
+        <v>0.250719</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.769641</v>
@@ -1959,19 +1959,19 @@
         <v>1.113983</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.572311</v>
+        <v>1.1132</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.415</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>10.256</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>26.46</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>48.418</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0</v>
@@ -2439,19 +2439,19 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.694689</v>
+        <v>0.1538</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>8.875999999999999</v>
+        <v>6.461</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>20.715</v>
+        <v>10.459</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>59.969</v>
+        <v>33.509</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>83.949</v>
+        <v>35.531</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>55.832</v>
@@ -4570,22 +4570,22 @@
         <v>7.216131</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>4.522818</v>
+        <v>4.523</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>16.226</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>46.035</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>148.911</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>229.028</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>300.369</v>
       </c>
     </row>
     <row r="101">
@@ -5530,22 +5530,22 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.202</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.964</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-1.654</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>-165.292</v>
+        <v>-170.037</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-502.403</v>
+        <v>-513.855</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-110.097</v>
+        <v>-126.257</v>
       </c>
     </row>
     <row r="125">
@@ -5570,22 +5570,22 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.202</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.964</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-1.654</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>196.111</v>
+        <v>191.366</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>371.939</v>
+        <v>360.487</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-110.097</v>
+        <v>-126.257</v>
       </c>
     </row>
     <row r="126">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -19523,7 +19523,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E198" s="5" t="n">
@@ -21882,7 +21882,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -23337,7 +23337,11 @@
           <t>Lease payments (note 8)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -26269,7 +26273,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -27588,7 +27592,11 @@
           <t>Lease payments (note 9)</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -28225,7 +28233,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -38536,7 +38544,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -41141,7 +41149,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -43393,7 +43401,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -53070,7 +53078,7 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
